--- a/ParticleSystem_database.xlsx
+++ b/ParticleSystem_database.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1577"/>
+  <dimension ref="A1:I1584"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46151,10 +46151,8 @@
       </c>
     </row>
     <row r="1577">
-      <c r="A1577" t="inlineStr">
-        <is>
-          <t>00002637</t>
-        </is>
+      <c r="A1577" t="n">
+        <v>2637</v>
       </c>
       <c r="B1577" t="n">
         <v>0.4</v>
@@ -46179,6 +46177,211 @@
       </c>
       <c r="I1577" t="n">
         <v>5000000</v>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="n">
+        <v>2638</v>
+      </c>
+      <c r="B1578" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C1578" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="D1578" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E1578" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F1578" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1578" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1578" t="n">
+        <v>4025</v>
+      </c>
+      <c r="I1578" t="n">
+        <v>1e+18</v>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="n">
+        <v>2639</v>
+      </c>
+      <c r="B1579" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C1579" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="D1579" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E1579" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F1579" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1579" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1579" t="n">
+        <v>4023</v>
+      </c>
+      <c r="I1579" t="n">
+        <v>1e+18</v>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="n">
+        <v>2640</v>
+      </c>
+      <c r="B1580" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C1580" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="D1580" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E1580" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F1580" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1580" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1580" t="n">
+        <v>4038</v>
+      </c>
+      <c r="I1580" t="n">
+        <v>1e+18</v>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="n">
+        <v>2641</v>
+      </c>
+      <c r="B1581" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C1581" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="D1581" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E1581" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F1581" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1581" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1581" t="n">
+        <v>4011</v>
+      </c>
+      <c r="I1581" t="n">
+        <v>1e+18</v>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="n">
+        <v>2642</v>
+      </c>
+      <c r="B1582" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C1582" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="D1582" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E1582" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F1582" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1582" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1582" t="n">
+        <v>3998</v>
+      </c>
+      <c r="I1582" t="n">
+        <v>1e+18</v>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="n">
+        <v>2643</v>
+      </c>
+      <c r="B1583" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C1583" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="D1583" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E1583" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F1583" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1583" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1583" t="n">
+        <v>4052</v>
+      </c>
+      <c r="I1583" t="n">
+        <v>1e+18</v>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="inlineStr">
+        <is>
+          <t>00002644</t>
+        </is>
+      </c>
+      <c r="B1584" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C1584" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="D1584" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E1584" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F1584" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1584" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1584" t="n">
+        <v>4058</v>
+      </c>
+      <c r="I1584" t="n">
+        <v>1e+18</v>
       </c>
     </row>
   </sheetData>

--- a/ParticleSystem_database.xlsx
+++ b/ParticleSystem_database.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1577"/>
+  <dimension ref="A1:I1584"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46151,10 +46151,8 @@
       </c>
     </row>
     <row r="1577">
-      <c r="A1577" t="inlineStr">
-        <is>
-          <t>00002637</t>
-        </is>
+      <c r="A1577" t="n">
+        <v>2637</v>
       </c>
       <c r="B1577" t="n">
         <v>0.4</v>
@@ -46179,6 +46177,211 @@
       </c>
       <c r="I1577" t="n">
         <v>5000000</v>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="n">
+        <v>2639</v>
+      </c>
+      <c r="B1578" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C1578" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="D1578" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E1578" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F1578" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1578" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1578" t="n">
+        <v>3939</v>
+      </c>
+      <c r="I1578" t="n">
+        <v>1e+18</v>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="n">
+        <v>2640</v>
+      </c>
+      <c r="B1579" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C1579" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="D1579" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E1579" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F1579" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1579" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1579" t="n">
+        <v>3951</v>
+      </c>
+      <c r="I1579" t="n">
+        <v>1e+18</v>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="n">
+        <v>2641</v>
+      </c>
+      <c r="B1580" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C1580" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="D1580" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E1580" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F1580" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1580" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1580" t="n">
+        <v>3961</v>
+      </c>
+      <c r="I1580" t="n">
+        <v>1e+18</v>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="n">
+        <v>2642</v>
+      </c>
+      <c r="B1581" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C1581" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="D1581" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E1581" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F1581" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1581" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1581" t="n">
+        <v>16002</v>
+      </c>
+      <c r="I1581" t="n">
+        <v>1e+18</v>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="n">
+        <v>2643</v>
+      </c>
+      <c r="B1582" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C1582" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="D1582" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E1582" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F1582" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1582" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1582" t="n">
+        <v>15777</v>
+      </c>
+      <c r="I1582" t="n">
+        <v>1e+18</v>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="n">
+        <v>2644</v>
+      </c>
+      <c r="B1583" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C1583" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="D1583" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E1583" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F1583" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1583" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1583" t="n">
+        <v>15852</v>
+      </c>
+      <c r="I1583" t="n">
+        <v>1e+18</v>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="inlineStr">
+        <is>
+          <t>00002645</t>
+        </is>
+      </c>
+      <c r="B1584" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C1584" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="D1584" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E1584" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F1584" t="n">
+        <v>150</v>
+      </c>
+      <c r="G1584" t="n">
+        <v>150</v>
+      </c>
+      <c r="H1584" t="n">
+        <v>9007</v>
+      </c>
+      <c r="I1584" t="n">
+        <v>1e+18</v>
       </c>
     </row>
   </sheetData>
